--- a/artfynd/Björnberget SV artfynd.xlsx
+++ b/artfynd/Björnberget SV artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99691</v>
+        <v>2056629</v>
       </c>
       <c r="B2" t="n">
-        <v>78647</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686297</v>
+        <v>685987</v>
       </c>
       <c r="R2" t="n">
-        <v>7091543</v>
+        <v>7091795</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,14 +757,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>tallnaturskog</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120148044</v>
+        <v>69298873</v>
       </c>
       <c r="B3" t="n">
-        <v>92551</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686213</v>
+        <v>686026</v>
       </c>
       <c r="R3" t="n">
-        <v>7092592</v>
+        <v>7092622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2017-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2017-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,64 +863,87 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallåga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120148046</v>
+        <v>7242848</v>
       </c>
       <c r="B4" t="n">
-        <v>92563</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686186</v>
+        <v>685785</v>
       </c>
       <c r="R4" t="n">
-        <v>7092609</v>
+        <v>7092026</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -944,12 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2013-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2013-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,26 +983,43 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>lövbarr</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asp</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Westling, Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>402318</v>
+        <v>1921682</v>
       </c>
       <c r="B5" t="n">
-        <v>82792</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686068</v>
+        <v>686001</v>
       </c>
       <c r="R5" t="n">
-        <v>7091795</v>
+        <v>7091971</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1058,14 +1098,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>gransumpskog</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2056629</v>
+        <v>1921683</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685987</v>
+        <v>685955</v>
       </c>
       <c r="R6" t="n">
-        <v>7091795</v>
+        <v>7091956</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99690</v>
+        <v>1921688</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686314</v>
+        <v>686001</v>
       </c>
       <c r="R7" t="n">
-        <v>7091516</v>
+        <v>7092621</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,14 +1302,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>tallnaturskog</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1292,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53620894</v>
+        <v>2056627</v>
       </c>
       <c r="B8" t="n">
-        <v>58027</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,48 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Abborrtjärn, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686072</v>
+        <v>685955</v>
       </c>
       <c r="R8" t="n">
-        <v>7091780</v>
+        <v>7091956</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,27 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-05-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I bäckskogsmiljö</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,26 +1403,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53620875</v>
+        <v>2056628</v>
       </c>
       <c r="B9" t="n">
-        <v>57646</v>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1426,48 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102119</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Abborrtjärn, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686072</v>
+        <v>686001</v>
       </c>
       <c r="R9" t="n">
-        <v>7091780</v>
+        <v>7091971</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,27 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-05-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-05-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Från tall efter vägen inne i byn</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,26 +1505,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2056627</v>
+        <v>1932904</v>
       </c>
       <c r="B10" t="n">
-        <v>80112</v>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120148049</v>
+        <v>1932906</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,37 +1639,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686098</v>
+        <v>686001</v>
       </c>
       <c r="R11" t="n">
-        <v>7092640</v>
+        <v>7092621</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,12 +1693,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,26 +1709,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1921683</v>
+        <v>99690</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1772,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685955</v>
+        <v>686314</v>
       </c>
       <c r="R12" t="n">
-        <v>7091956</v>
+        <v>7091516</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1819,9 +1812,14 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>tallnaturskog</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1839,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15769924</v>
+        <v>99691</v>
       </c>
       <c r="B13" t="n">
-        <v>5492</v>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,37 +1848,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Abborrtjärn, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686072</v>
+        <v>686297</v>
       </c>
       <c r="R13" t="n">
-        <v>7091780</v>
+        <v>7091543</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,22 +1902,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2013-06-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2013-06-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,28 +1921,33 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>tallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Niina Sallmén</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69298873</v>
+        <v>402318</v>
       </c>
       <c r="B14" t="n">
-        <v>78647</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,13 +1979,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686026</v>
+        <v>686068</v>
       </c>
       <c r="R14" t="n">
-        <v>7092622</v>
+        <v>7091795</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,17 +2009,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-10-23</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-10-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,68 +2028,55 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
+          <t>gransumpskog</t>
+        </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga # Pinus sylvestris</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1932904</v>
+        <v>402319</v>
       </c>
       <c r="B15" t="n">
-        <v>80118</v>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685955</v>
+        <v>686041</v>
       </c>
       <c r="R15" t="n">
-        <v>7091956</v>
+        <v>7091800</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2158,9 +2133,14 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>gransumpskog</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2178,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>402319</v>
+        <v>7242834</v>
       </c>
       <c r="B16" t="n">
-        <v>82792</v>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2169,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Abborrtjärn, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686041</v>
+        <v>686072</v>
       </c>
       <c r="R16" t="n">
-        <v>7091800</v>
+        <v>7091780</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,12 +2223,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2013-06-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2013-06-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2262,71 +2242,78 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>gransumpskog</t>
-        </is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>1 substratenheter # tallåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Ulrika Westling, Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1921682</v>
+        <v>133307196</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>80367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Grundtjärnmyran, Grundtjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686001</v>
+        <v>686436</v>
       </c>
       <c r="R17" t="n">
-        <v>7091971</v>
+        <v>7091482</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2350,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,69 +2353,64 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2056628</v>
+        <v>15769924</v>
       </c>
       <c r="B18" t="n">
-        <v>80112</v>
+        <v>5495</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>101410</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Abborrtjärn, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686001</v>
+        <v>686072</v>
       </c>
       <c r="R18" t="n">
-        <v>7091971</v>
+        <v>7091780</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2452,12 +2434,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2013-06-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2013-06-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,30 +2451,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>sälg</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Via Niina Sallmén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7242834</v>
+        <v>53620875</v>
       </c>
       <c r="B19" t="n">
-        <v>92727</v>
+        <v>57942</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,24 +2482,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>102119</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Abborrtjärn, Ång</t>
@@ -2554,12 +2547,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2013-06-12</t>
+          <t>2015-05-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2013-06-12</t>
+          <t>2015-05-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Från tall efter vägen inne i byn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2570,43 +2578,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>1 substratenheter # tallåga</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Ulf Hallin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7242848</v>
+        <v>53620894</v>
       </c>
       <c r="B20" t="n">
-        <v>91256</v>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,37 +2605,48 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Abborrtjärn, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685785</v>
+        <v>686072</v>
       </c>
       <c r="R20" t="n">
-        <v>7092026</v>
+        <v>7091780</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2668,12 +2670,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2013-06-11</t>
+          <t>2015-05-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2013-06-11</t>
+          <t>2015-05-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I bäckskogsmiljö</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,43 +2701,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>lövbarr</t>
-        </is>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asp</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Ulf Hallin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120148047</v>
+        <v>30889</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>56689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,37 +2728,51 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>206046</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686099</v>
+        <v>686412</v>
       </c>
       <c r="R21" t="n">
-        <v>7092577</v>
+        <v>7091398</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2782,12 +2796,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2008-08-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,60 +2816,64 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120148048</v>
+        <v>133306304</v>
       </c>
       <c r="B22" t="n">
-        <v>92527</v>
+        <v>99178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärnmyran, Grundtjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686115</v>
+        <v>686388</v>
       </c>
       <c r="R22" t="n">
-        <v>7092614</v>
+        <v>7091381</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2879,12 +2897,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,22 +2917,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1932906</v>
+        <v>5978371</v>
       </c>
       <c r="B23" t="n">
-        <v>80118</v>
+        <v>99038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,23 +2940,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2946,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686001</v>
+        <v>686090</v>
       </c>
       <c r="R23" t="n">
-        <v>7092621</v>
+        <v>7091813</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2992,11 +3006,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3013,45 +3022,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120148045</v>
+        <v>66210764</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>80299</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>385</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget-Gäddtjärnen NR, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686190</v>
+        <v>686414</v>
       </c>
       <c r="R24" t="n">
-        <v>7092587</v>
+        <v>7092570</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3087,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2017-06-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2017-06-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,64 +3103,69 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1921688</v>
+        <v>120148044</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>93213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686001</v>
+        <v>686213</v>
       </c>
       <c r="R25" t="n">
-        <v>7092621</v>
+        <v>7092592</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3175,12 +3189,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2008-08-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,24 +3205,713 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120148048</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bjurholm, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>686115</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7092614</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120148049</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bjurholm, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>686098</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7092640</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>66210761</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Björnberget-Gäddtjärnen NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>686409</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7092565</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120148047</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bjurholm, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>686099</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7092577</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>66210763</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björnberget-Gäddtjärnen NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>686411</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7092566</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>66210765</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Björnberget-Gäddtjärnen NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>686414</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7092570</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120148045</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bjurholm, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>686190</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7092587</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Björnberget SV artfynd.xlsx
+++ b/artfynd/Björnberget SV artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2275,7 +2275,7 @@
         <v>133307196</v>
       </c>
       <c r="B17" t="n">
-        <v>80367</v>
+        <v>80382</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>133306304</v>
       </c>
       <c r="B22" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3818,45 +3818,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120148045</v>
+        <v>134790678</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>57796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>102976</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget-Gäddtjärnen NR, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686190</v>
+        <v>686391</v>
       </c>
       <c r="R32" t="n">
-        <v>7092587</v>
+        <v>7092561</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,12 +3892,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3903,15 +3922,112 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120148045</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bjurholm, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>686190</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7092587</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Hanna Bäckman</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Hanna Bäckman</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
